--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.01548606378302</v>
+        <v>9.91501648536474</v>
       </c>
       <c r="D2" t="n">
-        <v>28.84566210407071</v>
+        <v>4.687420091911491</v>
       </c>
       <c r="E2" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F2" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.40280457466515</v>
+        <v>6.727955743383088</v>
       </c>
       <c r="D3" t="n">
-        <v>33.43840643191653</v>
+        <v>5.433741045186437</v>
       </c>
       <c r="E3" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F3" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.56894578091808</v>
+        <v>8.867453689399188</v>
       </c>
       <c r="D4" t="n">
-        <v>41.69339142944463</v>
+        <v>6.775176107284753</v>
       </c>
       <c r="E4" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F4" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.80842908354091</v>
+        <v>7.606369726075399</v>
       </c>
       <c r="D5" t="n">
-        <v>47.71125386487726</v>
+        <v>7.753078753042555</v>
       </c>
       <c r="E5" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F5" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.65008722509325</v>
+        <v>9.855639174077654</v>
       </c>
       <c r="D6" t="n">
-        <v>59.88181045846582</v>
+        <v>9.730794199500696</v>
       </c>
       <c r="E6" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F6" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.31537039857081</v>
+        <v>8.988747689767756</v>
       </c>
       <c r="D7" t="n">
-        <v>54.42755495602957</v>
+        <v>8.844477680354805</v>
       </c>
       <c r="E7" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F7" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>63.9519905113003</v>
+        <v>10.3921984580863</v>
       </c>
       <c r="D8" t="n">
-        <v>62.93542501766363</v>
+        <v>10.22700656537034</v>
       </c>
       <c r="E8" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F8" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.03201663924693</v>
+        <v>5.042702703877626</v>
       </c>
       <c r="D9" t="n">
-        <v>31.55085536681291</v>
+        <v>5.127013997107098</v>
       </c>
       <c r="E9" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F9" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.61418394859339</v>
+        <v>7.899804891646426</v>
       </c>
       <c r="D10" t="n">
-        <v>48.148403124799</v>
+        <v>7.824115507779839</v>
       </c>
       <c r="E10" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F10" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.45268476600287</v>
+        <v>7.711061274475466</v>
       </c>
       <c r="D11" t="n">
-        <v>46.25094857112769</v>
+        <v>7.515779142808251</v>
       </c>
       <c r="E11" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F11" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>43.52230706310463</v>
+        <v>7.072374897754504</v>
       </c>
       <c r="D12" t="n">
-        <v>42.36044759978731</v>
+        <v>6.883572734965439</v>
       </c>
       <c r="E12" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F12" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.52813895725598</v>
+        <v>5.773322580554098</v>
       </c>
       <c r="D13" t="n">
-        <v>35.28404945258097</v>
+        <v>5.733658036044408</v>
       </c>
       <c r="E13" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F13" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>23.61870584176781</v>
+        <v>3.838039699287269</v>
       </c>
       <c r="D14" t="n">
-        <v>22.1040196005372</v>
+        <v>3.591903185087295</v>
       </c>
       <c r="E14" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F14" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23.86916094622827</v>
+        <v>3.878738653762094</v>
       </c>
       <c r="D15" t="n">
-        <v>24.85720529028467</v>
+        <v>4.03929585967126</v>
       </c>
       <c r="E15" t="n">
-        <v>12.76344133458569</v>
+        <v>2.074059216870175</v>
       </c>
       <c r="F15" t="n">
-        <v>12.2076938951072</v>
+        <v>1.98375025795492</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
